--- a/Data/EXCEL/Transfer/salemon/202208/4766-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/4766-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E14F0AC4-ABD2-40CF-93B3-FEB120784F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE27F376-595B-435E-9462-590301108781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="4766-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,21 +1226,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="14.25" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,2445 +1393,2445 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>132.5</v>
+        <v>133</v>
       </c>
       <c r="C5" s="7">
-        <v>132</v>
+        <v>141.5</v>
       </c>
       <c r="D5" s="7">
-        <v>135.5</v>
+        <v>144.5</v>
       </c>
       <c r="E5" s="7">
-        <v>127</v>
+        <v>127.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-0.5</v>
+        <v>9.5</v>
       </c>
       <c r="G5" s="8">
-        <v>-0.38</v>
+        <v>7.2</v>
       </c>
       <c r="H5" s="9">
-        <v>18.829999999999998</v>
-      </c>
-      <c r="I5" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="J5" s="10">
+        <v>19.93</v>
+      </c>
+      <c r="I5" s="8">
+        <v>5.85</v>
+      </c>
+      <c r="J5" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="K5" s="9">
+        <v>144.30000000000001</v>
+      </c>
+      <c r="L5" s="8">
         <v>23</v>
       </c>
-      <c r="K5" s="9">
-        <v>124.4</v>
-      </c>
-      <c r="L5" s="10">
-        <v>19.399999999999999</v>
-      </c>
       <c r="M5" s="9">
-        <v>18.829999999999998</v>
-      </c>
-      <c r="N5" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="O5" s="10">
+        <v>19.93</v>
+      </c>
+      <c r="N5" s="8">
+        <v>5.85</v>
+      </c>
+      <c r="O5" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="P5" s="9">
+        <v>144.30000000000001</v>
+      </c>
+      <c r="Q5" s="8">
         <v>23</v>
-      </c>
-      <c r="P5" s="9">
-        <v>124.4</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>135</v>
+        <v>132.5</v>
       </c>
       <c r="C6" s="7">
-        <v>132.5</v>
+        <v>132</v>
       </c>
       <c r="D6" s="7">
-        <v>138</v>
+        <v>135.5</v>
       </c>
       <c r="E6" s="7">
         <v>127</v>
       </c>
-      <c r="F6" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G6" s="8">
-        <v>-1.85</v>
+      <c r="F6" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-0.38</v>
       </c>
       <c r="H6" s="9">
-        <v>18.46</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="I6" s="8">
-        <v>-3.03</v>
-      </c>
-      <c r="J6" s="10">
-        <v>14.8</v>
+        <v>1.99</v>
+      </c>
+      <c r="J6" s="8">
+        <v>23</v>
       </c>
       <c r="K6" s="9">
-        <v>105.6</v>
-      </c>
-      <c r="L6" s="10">
-        <v>18.7</v>
+        <v>124.4</v>
+      </c>
+      <c r="L6" s="8">
+        <v>19.399999999999999</v>
       </c>
       <c r="M6" s="9">
-        <v>18.46</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="N6" s="8">
-        <v>-3.03</v>
-      </c>
-      <c r="O6" s="10">
-        <v>14.8</v>
+        <v>1.99</v>
+      </c>
+      <c r="O6" s="8">
+        <v>23</v>
       </c>
       <c r="P6" s="9">
-        <v>105.6</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>18.7</v>
+        <v>124.4</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C7" s="7">
-        <v>135</v>
+        <v>132.5</v>
       </c>
       <c r="D7" s="7">
-        <v>138.5</v>
+        <v>138</v>
       </c>
       <c r="E7" s="7">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F7" s="10">
-        <v>12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G7" s="10">
-        <v>10.199999999999999</v>
+        <v>-1.85</v>
       </c>
       <c r="H7" s="9">
-        <v>19.04</v>
+        <v>18.46</v>
       </c>
       <c r="I7" s="10">
-        <v>2.29</v>
-      </c>
-      <c r="J7" s="10">
-        <v>32.700000000000003</v>
+        <v>-3.03</v>
+      </c>
+      <c r="J7" s="8">
+        <v>14.8</v>
       </c>
       <c r="K7" s="9">
-        <v>87.13</v>
-      </c>
-      <c r="L7" s="10">
-        <v>19.600000000000001</v>
+        <v>105.6</v>
+      </c>
+      <c r="L7" s="8">
+        <v>18.7</v>
       </c>
       <c r="M7" s="9">
-        <v>19.04</v>
+        <v>18.46</v>
       </c>
       <c r="N7" s="10">
-        <v>2.29</v>
-      </c>
-      <c r="O7" s="10">
-        <v>32.700000000000003</v>
+        <v>-3.03</v>
+      </c>
+      <c r="O7" s="8">
+        <v>14.8</v>
       </c>
       <c r="P7" s="9">
-        <v>87.13</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>19.600000000000001</v>
+        <v>105.6</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>18.7</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C8" s="7">
-        <v>122.5</v>
+        <v>135</v>
       </c>
       <c r="D8" s="7">
-        <v>131.5</v>
+        <v>138.5</v>
       </c>
       <c r="E8" s="7">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F8" s="8">
-        <v>-8</v>
+        <v>12.5</v>
       </c>
       <c r="G8" s="8">
-        <v>-6.13</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H8" s="9">
-        <v>18.61</v>
+        <v>19.04</v>
       </c>
       <c r="I8" s="8">
-        <v>-5.8</v>
-      </c>
-      <c r="J8" s="10">
+        <v>2.29</v>
+      </c>
+      <c r="J8" s="8">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="K8" s="9">
+        <v>87.13</v>
+      </c>
+      <c r="L8" s="8">
         <v>19.600000000000001</v>
       </c>
-      <c r="K8" s="9">
-        <v>68.09</v>
-      </c>
-      <c r="L8" s="10">
-        <v>16.399999999999999</v>
-      </c>
       <c r="M8" s="9">
-        <v>18.61</v>
+        <v>19.04</v>
       </c>
       <c r="N8" s="8">
-        <v>-5.8</v>
-      </c>
-      <c r="O8" s="10">
+        <v>2.29</v>
+      </c>
+      <c r="O8" s="8">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="P8" s="9">
+        <v>87.13</v>
+      </c>
+      <c r="Q8" s="8">
         <v>19.600000000000001</v>
-      </c>
-      <c r="P8" s="9">
-        <v>68.09</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="7">
-        <v>130.5</v>
+        <v>122.5</v>
       </c>
       <c r="D9" s="7">
-        <v>137.5</v>
+        <v>131.5</v>
       </c>
       <c r="E9" s="7">
-        <v>127.5</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-3.5</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-2.61</v>
+        <v>120</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-8</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-6.13</v>
       </c>
       <c r="H9" s="9">
-        <v>19.760000000000002</v>
+        <v>18.61</v>
       </c>
       <c r="I9" s="10">
-        <v>47.7</v>
-      </c>
-      <c r="J9" s="10">
-        <v>16.3</v>
+        <v>-5.8</v>
+      </c>
+      <c r="J9" s="8">
+        <v>19.600000000000001</v>
       </c>
       <c r="K9" s="9">
-        <v>49.48</v>
-      </c>
-      <c r="L9" s="10">
-        <v>15.2</v>
+        <v>68.09</v>
+      </c>
+      <c r="L9" s="8">
+        <v>16.399999999999999</v>
       </c>
       <c r="M9" s="9">
-        <v>19.760000000000002</v>
+        <v>18.61</v>
       </c>
       <c r="N9" s="10">
-        <v>47.7</v>
-      </c>
-      <c r="O9" s="10">
-        <v>16.3</v>
+        <v>-5.8</v>
+      </c>
+      <c r="O9" s="8">
+        <v>19.600000000000001</v>
       </c>
       <c r="P9" s="9">
-        <v>49.48</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>15.2</v>
+        <v>68.09</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>139.5</v>
+        <v>134</v>
       </c>
       <c r="C10" s="7">
-        <v>134</v>
+        <v>130.5</v>
       </c>
       <c r="D10" s="7">
-        <v>139.5</v>
+        <v>137.5</v>
       </c>
       <c r="E10" s="7">
-        <v>133.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>-5</v>
-      </c>
-      <c r="G10" s="8">
-        <v>-3.6</v>
+        <v>127.5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-3.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>-2.61</v>
       </c>
       <c r="H10" s="9">
-        <v>13.38</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="I10" s="8">
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="J10" s="10">
-        <v>39.5</v>
+        <v>47.7</v>
+      </c>
+      <c r="J10" s="8">
+        <v>16.3</v>
       </c>
       <c r="K10" s="9">
-        <v>29.72</v>
-      </c>
-      <c r="L10" s="10">
-        <v>14.6</v>
+        <v>49.48</v>
+      </c>
+      <c r="L10" s="8">
+        <v>15.2</v>
       </c>
       <c r="M10" s="9">
-        <v>13.38</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="N10" s="8">
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="O10" s="10">
-        <v>39.5</v>
+        <v>47.7</v>
+      </c>
+      <c r="O10" s="8">
+        <v>16.3</v>
       </c>
       <c r="P10" s="9">
-        <v>29.72</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>14.6</v>
+        <v>49.48</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>15.2</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>142</v>
+        <v>139.5</v>
       </c>
       <c r="C11" s="7">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D11" s="7">
-        <v>145</v>
+        <v>139.5</v>
       </c>
       <c r="E11" s="7">
-        <v>136</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-2.11</v>
+        <v>133.5</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-5</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-3.6</v>
       </c>
       <c r="H11" s="9">
-        <v>16.34</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-3.37</v>
+        <v>13.38</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="J11" s="8">
-        <v>-0.04</v>
+        <v>39.5</v>
       </c>
       <c r="K11" s="9">
-        <v>16.34</v>
+        <v>29.72</v>
       </c>
       <c r="L11" s="8">
-        <v>-0.04</v>
+        <v>14.6</v>
       </c>
       <c r="M11" s="9">
-        <v>16.34</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-3.37</v>
+        <v>13.38</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-18.100000000000001</v>
       </c>
       <c r="O11" s="8">
-        <v>-0.04</v>
+        <v>39.5</v>
       </c>
       <c r="P11" s="9">
-        <v>16.34</v>
+        <v>29.72</v>
       </c>
       <c r="Q11" s="8">
-        <v>-0.04</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>140.5</v>
+        <v>142</v>
       </c>
       <c r="C12" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D12" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E12" s="7">
-        <v>137.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-1.73</v>
+        <v>136</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-3</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-2.11</v>
       </c>
       <c r="H12" s="9">
-        <v>16.91</v>
-      </c>
-      <c r="I12" s="8">
-        <v>-0.93</v>
+        <v>16.34</v>
+      </c>
+      <c r="I12" s="10">
+        <v>-3.37</v>
       </c>
       <c r="J12" s="10">
-        <v>11.6</v>
+        <v>-0.04</v>
       </c>
       <c r="K12" s="9">
-        <v>179.8</v>
+        <v>16.34</v>
       </c>
       <c r="L12" s="10">
-        <v>15.6</v>
+        <v>-0.04</v>
       </c>
       <c r="M12" s="9">
-        <v>16.91</v>
-      </c>
-      <c r="N12" s="8">
-        <v>-0.93</v>
+        <v>16.34</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-3.37</v>
       </c>
       <c r="O12" s="10">
-        <v>11.6</v>
+        <v>-0.04</v>
       </c>
       <c r="P12" s="9">
-        <v>179.8</v>
+        <v>16.34</v>
       </c>
       <c r="Q12" s="10">
-        <v>15.6</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>138</v>
+        <v>140.5</v>
       </c>
       <c r="C13" s="7">
-        <v>144.5</v>
+        <v>142</v>
       </c>
       <c r="D13" s="7">
-        <v>144.5</v>
+        <v>142</v>
       </c>
       <c r="E13" s="7">
-        <v>135</v>
+        <v>137.5</v>
       </c>
       <c r="F13" s="10">
-        <v>5.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G13" s="10">
-        <v>3.96</v>
+        <v>-1.73</v>
       </c>
       <c r="H13" s="9">
-        <v>17.07</v>
+        <v>16.91</v>
       </c>
       <c r="I13" s="10">
-        <v>15.2</v>
-      </c>
-      <c r="J13" s="10">
-        <v>13</v>
+        <v>-0.93</v>
+      </c>
+      <c r="J13" s="8">
+        <v>11.6</v>
       </c>
       <c r="K13" s="9">
-        <v>162.9</v>
-      </c>
-      <c r="L13" s="10">
-        <v>16</v>
+        <v>179.8</v>
+      </c>
+      <c r="L13" s="8">
+        <v>15.6</v>
       </c>
       <c r="M13" s="9">
-        <v>17.07</v>
+        <v>16.91</v>
       </c>
       <c r="N13" s="10">
-        <v>15.2</v>
-      </c>
-      <c r="O13" s="10">
-        <v>13</v>
+        <v>-0.93</v>
+      </c>
+      <c r="O13" s="8">
+        <v>11.6</v>
       </c>
       <c r="P13" s="9">
-        <v>162.9</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>16</v>
+        <v>179.8</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>15.6</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>137.5</v>
+        <v>138</v>
       </c>
       <c r="C14" s="7">
-        <v>139</v>
+        <v>144.5</v>
       </c>
       <c r="D14" s="7">
-        <v>141</v>
+        <v>144.5</v>
       </c>
       <c r="E14" s="7">
         <v>135</v>
       </c>
-      <c r="F14" s="10">
-        <v>1</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.72</v>
+      <c r="F14" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="G14" s="8">
+        <v>3.96</v>
       </c>
       <c r="H14" s="9">
-        <v>14.82</v>
-      </c>
-      <c r="I14" s="10">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J14" s="10">
-        <v>3.25</v>
+        <v>17.07</v>
+      </c>
+      <c r="I14" s="8">
+        <v>15.2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>13</v>
       </c>
       <c r="K14" s="9">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="L14" s="10">
-        <v>16.399999999999999</v>
+        <v>162.9</v>
+      </c>
+      <c r="L14" s="8">
+        <v>16</v>
       </c>
       <c r="M14" s="9">
-        <v>14.82</v>
-      </c>
-      <c r="N14" s="10">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="O14" s="10">
-        <v>3.25</v>
+        <v>17.07</v>
+      </c>
+      <c r="N14" s="8">
+        <v>15.2</v>
+      </c>
+      <c r="O14" s="8">
+        <v>13</v>
       </c>
       <c r="P14" s="9">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>16.399999999999999</v>
+        <v>162.9</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
+        <v>137.5</v>
+      </c>
+      <c r="C15" s="7">
+        <v>139</v>
+      </c>
+      <c r="D15" s="7">
         <v>141</v>
       </c>
-      <c r="C15" s="7">
-        <v>138</v>
-      </c>
-      <c r="D15" s="7">
-        <v>144</v>
-      </c>
       <c r="E15" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F15" s="8">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="8">
-        <v>-1.43</v>
+        <v>0.72</v>
       </c>
       <c r="H15" s="9">
-        <v>13.69</v>
-      </c>
-      <c r="I15" s="10">
-        <v>4.78</v>
+        <v>14.82</v>
+      </c>
+      <c r="I15" s="8">
+        <v>8.1999999999999993</v>
       </c>
       <c r="J15" s="8">
-        <v>-1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K15" s="9">
-        <v>131</v>
-      </c>
-      <c r="L15" s="10">
-        <v>18.100000000000001</v>
+        <v>145.80000000000001</v>
+      </c>
+      <c r="L15" s="8">
+        <v>16.399999999999999</v>
       </c>
       <c r="M15" s="9">
-        <v>13.69</v>
-      </c>
-      <c r="N15" s="10">
-        <v>4.78</v>
+        <v>14.82</v>
+      </c>
+      <c r="N15" s="8">
+        <v>8.1999999999999993</v>
       </c>
       <c r="O15" s="8">
-        <v>-1.03</v>
+        <v>3.25</v>
       </c>
       <c r="P15" s="9">
-        <v>131</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>18.100000000000001</v>
+        <v>145.80000000000001</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>150.5</v>
+        <v>141</v>
       </c>
       <c r="C16" s="7">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D16" s="7">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E16" s="7">
-        <v>135.5</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-10</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-6.67</v>
+        <v>137</v>
+      </c>
+      <c r="F16" s="10">
+        <v>-2</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-1.43</v>
       </c>
       <c r="H16" s="9">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="I16" s="8">
-        <v>-14.6</v>
+        <v>4.78</v>
       </c>
       <c r="J16" s="10">
-        <v>3.5</v>
+        <v>-1.03</v>
       </c>
       <c r="K16" s="9">
-        <v>117.3</v>
-      </c>
-      <c r="L16" s="10">
-        <v>20.8</v>
+        <v>131</v>
+      </c>
+      <c r="L16" s="8">
+        <v>18.100000000000001</v>
       </c>
       <c r="M16" s="9">
-        <v>13.07</v>
+        <v>13.69</v>
       </c>
       <c r="N16" s="8">
-        <v>-14.6</v>
+        <v>4.78</v>
       </c>
       <c r="O16" s="10">
-        <v>3.5</v>
+        <v>-1.03</v>
       </c>
       <c r="P16" s="9">
-        <v>117.3</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>20.8</v>
+        <v>131</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>156</v>
+        <v>150.5</v>
       </c>
       <c r="C17" s="7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D17" s="7">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="E17" s="7">
-        <v>148</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-5.5</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-3.54</v>
+        <v>135.5</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-10</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-6.67</v>
       </c>
       <c r="H17" s="9">
-        <v>15.31</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-4.8099999999999996</v>
-      </c>
-      <c r="J17" s="10">
-        <v>12.2</v>
+        <v>13.07</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="J17" s="8">
+        <v>3.5</v>
       </c>
       <c r="K17" s="9">
-        <v>104.2</v>
-      </c>
-      <c r="L17" s="10">
-        <v>23.4</v>
+        <v>117.3</v>
+      </c>
+      <c r="L17" s="8">
+        <v>20.8</v>
       </c>
       <c r="M17" s="9">
-        <v>15.31</v>
-      </c>
-      <c r="N17" s="8">
-        <v>-4.8099999999999996</v>
-      </c>
-      <c r="O17" s="10">
-        <v>12.2</v>
+        <v>13.07</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="O17" s="8">
+        <v>3.5</v>
       </c>
       <c r="P17" s="9">
-        <v>104.2</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>23.4</v>
+        <v>117.3</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>20.8</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C18" s="7">
-        <v>155.5</v>
+        <v>150</v>
       </c>
       <c r="D18" s="7">
-        <v>156</v>
+        <v>157.5</v>
       </c>
       <c r="E18" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F18" s="10">
-        <v>5</v>
+        <v>-5.5</v>
       </c>
       <c r="G18" s="10">
-        <v>3.32</v>
+        <v>-3.54</v>
       </c>
       <c r="H18" s="9">
-        <v>16.09</v>
+        <v>15.31</v>
       </c>
       <c r="I18" s="10">
-        <v>12.1</v>
-      </c>
-      <c r="J18" s="10">
-        <v>37.9</v>
+        <v>-4.8099999999999996</v>
+      </c>
+      <c r="J18" s="8">
+        <v>12.2</v>
       </c>
       <c r="K18" s="9">
-        <v>88.92</v>
-      </c>
-      <c r="L18" s="10">
-        <v>25.6</v>
+        <v>104.2</v>
+      </c>
+      <c r="L18" s="8">
+        <v>23.4</v>
       </c>
       <c r="M18" s="9">
-        <v>16.09</v>
+        <v>15.31</v>
       </c>
       <c r="N18" s="10">
-        <v>12.1</v>
-      </c>
-      <c r="O18" s="10">
-        <v>37.9</v>
+        <v>-4.8099999999999996</v>
+      </c>
+      <c r="O18" s="8">
+        <v>12.2</v>
       </c>
       <c r="P18" s="9">
-        <v>88.92</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>25.6</v>
+        <v>104.2</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>23.4</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>160.5</v>
+        <v>151</v>
       </c>
       <c r="C19" s="7">
-        <v>150.5</v>
+        <v>155.5</v>
       </c>
       <c r="D19" s="7">
-        <v>160.5</v>
+        <v>156</v>
       </c>
       <c r="E19" s="7">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="F19" s="8">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G19" s="8">
-        <v>-6.23</v>
+        <v>3.32</v>
       </c>
       <c r="H19" s="9">
-        <v>14.35</v>
+        <v>16.09</v>
       </c>
       <c r="I19" s="8">
-        <v>-7.81</v>
-      </c>
-      <c r="J19" s="10">
-        <v>42.5</v>
+        <v>12.1</v>
+      </c>
+      <c r="J19" s="8">
+        <v>37.9</v>
       </c>
       <c r="K19" s="9">
-        <v>72.83</v>
-      </c>
-      <c r="L19" s="10">
-        <v>23.2</v>
+        <v>88.92</v>
+      </c>
+      <c r="L19" s="8">
+        <v>25.6</v>
       </c>
       <c r="M19" s="9">
-        <v>14.35</v>
+        <v>16.09</v>
       </c>
       <c r="N19" s="8">
-        <v>-7.81</v>
-      </c>
-      <c r="O19" s="10">
-        <v>42.5</v>
+        <v>12.1</v>
+      </c>
+      <c r="O19" s="8">
+        <v>37.9</v>
       </c>
       <c r="P19" s="9">
-        <v>72.83</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>23.2</v>
+        <v>88.92</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>25.6</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
         <v>160.5</v>
       </c>
       <c r="C20" s="7">
+        <v>150.5</v>
+      </c>
+      <c r="D20" s="7">
         <v>160.5</v>
       </c>
-      <c r="D20" s="7">
-        <v>165.5</v>
-      </c>
       <c r="E20" s="7">
-        <v>156.5</v>
+        <v>132</v>
       </c>
       <c r="F20" s="10">
-        <v>0.5</v>
+        <v>-10</v>
       </c>
       <c r="G20" s="10">
-        <v>0.31</v>
+        <v>-6.23</v>
       </c>
       <c r="H20" s="9">
-        <v>15.56</v>
-      </c>
-      <c r="I20" s="8">
-        <v>-8.41</v>
-      </c>
-      <c r="J20" s="10">
-        <v>32.1</v>
+        <v>14.35</v>
+      </c>
+      <c r="I20" s="10">
+        <v>-7.81</v>
+      </c>
+      <c r="J20" s="8">
+        <v>42.5</v>
       </c>
       <c r="K20" s="9">
-        <v>58.49</v>
-      </c>
-      <c r="L20" s="10">
-        <v>19.2</v>
+        <v>72.83</v>
+      </c>
+      <c r="L20" s="8">
+        <v>23.2</v>
       </c>
       <c r="M20" s="9">
-        <v>15.56</v>
-      </c>
-      <c r="N20" s="8">
-        <v>-8.41</v>
-      </c>
-      <c r="O20" s="10">
-        <v>32.1</v>
+        <v>14.35</v>
+      </c>
+      <c r="N20" s="10">
+        <v>-7.81</v>
+      </c>
+      <c r="O20" s="8">
+        <v>42.5</v>
       </c>
       <c r="P20" s="9">
-        <v>58.49</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>19.2</v>
+        <v>72.83</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>23.2</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>162</v>
+        <v>160.5</v>
       </c>
       <c r="C21" s="7">
-        <v>160</v>
+        <v>160.5</v>
       </c>
       <c r="D21" s="7">
-        <v>165</v>
+        <v>165.5</v>
       </c>
       <c r="E21" s="7">
-        <v>155</v>
+        <v>156.5</v>
       </c>
       <c r="F21" s="8">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="8">
-        <v>-1.23</v>
+        <v>0.31</v>
       </c>
       <c r="H21" s="9">
-        <v>16.989999999999998</v>
+        <v>15.56</v>
       </c>
       <c r="I21" s="10">
-        <v>77.2</v>
-      </c>
-      <c r="J21" s="10">
-        <v>25</v>
+        <v>-8.41</v>
+      </c>
+      <c r="J21" s="8">
+        <v>32.1</v>
       </c>
       <c r="K21" s="9">
-        <v>42.93</v>
-      </c>
-      <c r="L21" s="10">
-        <v>15.1</v>
+        <v>58.49</v>
+      </c>
+      <c r="L21" s="8">
+        <v>19.2</v>
       </c>
       <c r="M21" s="9">
-        <v>16.989999999999998</v>
+        <v>15.56</v>
       </c>
       <c r="N21" s="10">
-        <v>77.2</v>
-      </c>
-      <c r="O21" s="10">
-        <v>25</v>
+        <v>-8.41</v>
+      </c>
+      <c r="O21" s="8">
+        <v>32.1</v>
       </c>
       <c r="P21" s="9">
-        <v>42.93</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>15.1</v>
+        <v>58.49</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>19.2</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>151.5</v>
+        <v>162</v>
       </c>
       <c r="C22" s="7">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D22" s="7">
-        <v>163.5</v>
+        <v>165</v>
       </c>
       <c r="E22" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F22" s="10">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="G22" s="10">
-        <v>6.58</v>
+        <v>-1.23</v>
       </c>
       <c r="H22" s="9">
-        <v>9.59</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="I22" s="8">
-        <v>-41.3</v>
+        <v>77.2</v>
       </c>
       <c r="J22" s="8">
-        <v>-20.3</v>
+        <v>25</v>
       </c>
       <c r="K22" s="9">
-        <v>25.94</v>
-      </c>
-      <c r="L22" s="10">
-        <v>9.43</v>
+        <v>42.93</v>
+      </c>
+      <c r="L22" s="8">
+        <v>15.1</v>
       </c>
       <c r="M22" s="9">
-        <v>9.59</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="N22" s="8">
-        <v>-41.3</v>
+        <v>77.2</v>
       </c>
       <c r="O22" s="8">
-        <v>-20.3</v>
+        <v>25</v>
       </c>
       <c r="P22" s="9">
-        <v>25.94</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>9.43</v>
+        <v>42.93</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>15.1</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>156</v>
+        <v>151.5</v>
       </c>
       <c r="C23" s="7">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D23" s="7">
-        <v>160.5</v>
+        <v>163.5</v>
       </c>
       <c r="E23" s="7">
         <v>150</v>
       </c>
       <c r="F23" s="8">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="G23" s="8">
-        <v>-2.56</v>
+        <v>6.58</v>
       </c>
       <c r="H23" s="9">
-        <v>16.350000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="I23" s="10">
-        <v>7.9</v>
+        <v>-41.3</v>
       </c>
       <c r="J23" s="10">
-        <v>40.1</v>
+        <v>-20.3</v>
       </c>
       <c r="K23" s="9">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="L23" s="10">
-        <v>40.1</v>
+        <v>25.94</v>
+      </c>
+      <c r="L23" s="8">
+        <v>9.43</v>
       </c>
       <c r="M23" s="9">
-        <v>16.350000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="N23" s="10">
-        <v>7.9</v>
+        <v>-41.3</v>
       </c>
       <c r="O23" s="10">
-        <v>40.1</v>
+        <v>-20.3</v>
       </c>
       <c r="P23" s="9">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>40.1</v>
+        <v>25.94</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>9.43</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="7">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D24" s="7">
-        <v>166</v>
+        <v>160.5</v>
       </c>
       <c r="E24" s="7">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F24" s="10">
-        <v>0.5</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="10">
-        <v>0.32</v>
+        <v>-2.56</v>
       </c>
       <c r="H24" s="9">
-        <v>15.15</v>
-      </c>
-      <c r="I24" s="10">
-        <v>0.32</v>
-      </c>
-      <c r="J24" s="10">
-        <v>4.54</v>
+        <v>16.350000000000001</v>
+      </c>
+      <c r="I24" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="J24" s="8">
+        <v>40.1</v>
       </c>
       <c r="K24" s="9">
-        <v>155.5</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="L24" s="8">
-        <v>-9.1300000000000008</v>
+        <v>40.1</v>
       </c>
       <c r="M24" s="9">
-        <v>15.15</v>
-      </c>
-      <c r="N24" s="10">
-        <v>0.32</v>
-      </c>
-      <c r="O24" s="10">
-        <v>4.54</v>
+        <v>16.350000000000001</v>
+      </c>
+      <c r="N24" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="O24" s="8">
+        <v>40.1</v>
       </c>
       <c r="P24" s="9">
-        <v>155.5</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="Q24" s="8">
-        <v>-9.1300000000000008</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C25" s="7">
+        <v>156</v>
+      </c>
+      <c r="D25" s="7">
+        <v>166</v>
+      </c>
+      <c r="E25" s="7">
+        <v>153</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="H25" s="9">
+        <v>15.15</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="J25" s="8">
+        <v>4.54</v>
+      </c>
+      <c r="K25" s="9">
         <v>155.5</v>
       </c>
-      <c r="D25" s="7">
-        <v>159</v>
-      </c>
-      <c r="E25" s="7">
-        <v>141</v>
-      </c>
-      <c r="F25" s="10">
-        <v>14.5</v>
-      </c>
-      <c r="G25" s="10">
-        <v>10.28</v>
-      </c>
-      <c r="H25" s="9">
-        <v>15.1</v>
-      </c>
-      <c r="I25" s="10">
-        <v>5.22</v>
-      </c>
-      <c r="J25" s="10">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="K25" s="9">
-        <v>140.4</v>
-      </c>
-      <c r="L25" s="8">
-        <v>-10.4</v>
+      <c r="L25" s="10">
+        <v>-9.1300000000000008</v>
       </c>
       <c r="M25" s="9">
-        <v>15.1</v>
-      </c>
-      <c r="N25" s="10">
-        <v>5.22</v>
-      </c>
-      <c r="O25" s="10">
-        <v>1.1299999999999999</v>
+        <v>15.15</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="O25" s="8">
+        <v>4.54</v>
       </c>
       <c r="P25" s="9">
-        <v>140.4</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>-10.4</v>
+        <v>155.5</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>-9.1300000000000008</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C26" s="7">
+        <v>155.5</v>
+      </c>
+      <c r="D26" s="7">
+        <v>159</v>
+      </c>
+      <c r="E26" s="7">
         <v>141</v>
       </c>
-      <c r="D26" s="7">
-        <v>148.5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>124</v>
-      </c>
-      <c r="F26" s="10">
-        <v>15.5</v>
-      </c>
-      <c r="G26" s="10">
-        <v>12.35</v>
+      <c r="F26" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="G26" s="8">
+        <v>10.28</v>
       </c>
       <c r="H26" s="9">
-        <v>14.35</v>
-      </c>
-      <c r="I26" s="10">
-        <v>3.71</v>
+        <v>15.1</v>
+      </c>
+      <c r="I26" s="8">
+        <v>5.22</v>
       </c>
       <c r="J26" s="8">
-        <v>-9.2899999999999991</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="K26" s="9">
-        <v>125.3</v>
-      </c>
-      <c r="L26" s="8">
-        <v>-11.6</v>
+        <v>140.4</v>
+      </c>
+      <c r="L26" s="10">
+        <v>-10.4</v>
       </c>
       <c r="M26" s="9">
-        <v>14.35</v>
-      </c>
-      <c r="N26" s="10">
-        <v>3.71</v>
+        <v>15.1</v>
+      </c>
+      <c r="N26" s="8">
+        <v>5.22</v>
       </c>
       <c r="O26" s="8">
-        <v>-9.2899999999999991</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P26" s="9">
-        <v>125.3</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>-11.6</v>
+        <v>140.4</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>-10.4</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27" s="7">
-        <v>125.5</v>
+        <v>141</v>
       </c>
       <c r="D27" s="7">
-        <v>130</v>
+        <v>148.5</v>
       </c>
       <c r="E27" s="7">
-        <v>123.5</v>
+        <v>124</v>
       </c>
       <c r="F27" s="8">
-        <v>-1.5</v>
+        <v>15.5</v>
       </c>
       <c r="G27" s="8">
-        <v>-1.18</v>
+        <v>12.35</v>
       </c>
       <c r="H27" s="9">
-        <v>13.84</v>
-      </c>
-      <c r="I27" s="10">
-        <v>9.59</v>
-      </c>
-      <c r="J27" s="8">
-        <v>-8.4499999999999993</v>
+        <v>14.35</v>
+      </c>
+      <c r="I27" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="J27" s="10">
+        <v>-9.2899999999999991</v>
       </c>
       <c r="K27" s="9">
-        <v>110.9</v>
-      </c>
-      <c r="L27" s="8">
-        <v>-11.9</v>
+        <v>125.3</v>
+      </c>
+      <c r="L27" s="10">
+        <v>-11.6</v>
       </c>
       <c r="M27" s="9">
-        <v>13.84</v>
-      </c>
-      <c r="N27" s="10">
-        <v>9.59</v>
-      </c>
-      <c r="O27" s="8">
-        <v>-8.4499999999999993</v>
+        <v>14.35</v>
+      </c>
+      <c r="N27" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="O27" s="10">
+        <v>-9.2899999999999991</v>
       </c>
       <c r="P27" s="9">
-        <v>110.9</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>-11.9</v>
+        <v>125.3</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>-11.6</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C28" s="7">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="D28" s="7">
-        <v>138.5</v>
+        <v>130</v>
       </c>
       <c r="E28" s="7">
-        <v>124</v>
-      </c>
-      <c r="F28" s="8">
-        <v>-10.5</v>
-      </c>
-      <c r="G28" s="8">
-        <v>-7.64</v>
+        <v>123.5</v>
+      </c>
+      <c r="F28" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G28" s="10">
+        <v>-1.18</v>
       </c>
       <c r="H28" s="9">
-        <v>12.63</v>
+        <v>13.84</v>
       </c>
       <c r="I28" s="8">
-        <v>-7.45</v>
-      </c>
-      <c r="J28" s="8">
-        <v>-14.6</v>
+        <v>9.59</v>
+      </c>
+      <c r="J28" s="10">
+        <v>-8.4499999999999993</v>
       </c>
       <c r="K28" s="9">
-        <v>97.07</v>
-      </c>
-      <c r="L28" s="8">
-        <v>-12.4</v>
+        <v>110.9</v>
+      </c>
+      <c r="L28" s="10">
+        <v>-11.9</v>
       </c>
       <c r="M28" s="9">
-        <v>12.63</v>
+        <v>13.84</v>
       </c>
       <c r="N28" s="8">
-        <v>-7.45</v>
-      </c>
-      <c r="O28" s="8">
-        <v>-14.6</v>
+        <v>9.59</v>
+      </c>
+      <c r="O28" s="10">
+        <v>-8.4499999999999993</v>
       </c>
       <c r="P28" s="9">
-        <v>97.07</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>-12.4</v>
+        <v>110.9</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>-11.9</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C29" s="7">
-        <v>137.5</v>
+        <v>127</v>
       </c>
       <c r="D29" s="7">
-        <v>142</v>
+        <v>138.5</v>
       </c>
       <c r="E29" s="7">
-        <v>133.5</v>
+        <v>124</v>
       </c>
       <c r="F29" s="10">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="G29" s="10">
-        <v>3.38</v>
+        <v>-7.64</v>
       </c>
       <c r="H29" s="9">
-        <v>13.64</v>
+        <v>12.63</v>
       </c>
       <c r="I29" s="10">
-        <v>17</v>
-      </c>
-      <c r="J29" s="8">
-        <v>-8.7200000000000006</v>
+        <v>-7.45</v>
+      </c>
+      <c r="J29" s="10">
+        <v>-14.6</v>
       </c>
       <c r="K29" s="9">
-        <v>84.44</v>
-      </c>
-      <c r="L29" s="8">
-        <v>-12</v>
+        <v>97.07</v>
+      </c>
+      <c r="L29" s="10">
+        <v>-12.4</v>
       </c>
       <c r="M29" s="9">
-        <v>13.64</v>
+        <v>12.63</v>
       </c>
       <c r="N29" s="10">
-        <v>17</v>
-      </c>
-      <c r="O29" s="8">
-        <v>-8.7200000000000006</v>
+        <v>-7.45</v>
+      </c>
+      <c r="O29" s="10">
+        <v>-14.6</v>
       </c>
       <c r="P29" s="9">
-        <v>84.44</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>-12</v>
+        <v>97.07</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>-12.4</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C30" s="7">
-        <v>133</v>
+        <v>137.5</v>
       </c>
       <c r="D30" s="7">
-        <v>144.5</v>
+        <v>142</v>
       </c>
       <c r="E30" s="7">
-        <v>129.5</v>
+        <v>133.5</v>
       </c>
       <c r="F30" s="8">
-        <v>-8</v>
+        <v>4.5</v>
       </c>
       <c r="G30" s="8">
-        <v>-5.67</v>
+        <v>3.38</v>
       </c>
       <c r="H30" s="9">
-        <v>11.66</v>
-      </c>
-      <c r="I30" s="10">
-        <v>15.9</v>
-      </c>
-      <c r="J30" s="8">
-        <v>-15.5</v>
+        <v>13.64</v>
+      </c>
+      <c r="I30" s="8">
+        <v>17</v>
+      </c>
+      <c r="J30" s="10">
+        <v>-8.7200000000000006</v>
       </c>
       <c r="K30" s="9">
-        <v>70.8</v>
-      </c>
-      <c r="L30" s="8">
-        <v>-12.6</v>
+        <v>84.44</v>
+      </c>
+      <c r="L30" s="10">
+        <v>-12</v>
       </c>
       <c r="M30" s="9">
-        <v>11.66</v>
-      </c>
-      <c r="N30" s="10">
-        <v>15.9</v>
-      </c>
-      <c r="O30" s="8">
-        <v>-15.5</v>
+        <v>13.64</v>
+      </c>
+      <c r="N30" s="8">
+        <v>17</v>
+      </c>
+      <c r="O30" s="10">
+        <v>-8.7200000000000006</v>
       </c>
       <c r="P30" s="9">
-        <v>70.8</v>
-      </c>
-      <c r="Q30" s="8">
-        <v>-12.6</v>
+        <v>84.44</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>-12</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>127.5</v>
+        <v>138</v>
       </c>
       <c r="C31" s="7">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D31" s="7">
-        <v>142</v>
+        <v>144.5</v>
       </c>
       <c r="E31" s="7">
-        <v>119</v>
+        <v>129.5</v>
       </c>
       <c r="F31" s="10">
-        <v>10.5</v>
+        <v>-8</v>
       </c>
       <c r="G31" s="10">
-        <v>8.0500000000000007</v>
+        <v>-5.67</v>
       </c>
       <c r="H31" s="9">
-        <v>10.07</v>
+        <v>11.66</v>
       </c>
       <c r="I31" s="8">
-        <v>-14.6</v>
-      </c>
-      <c r="J31" s="8">
-        <v>-32.799999999999997</v>
+        <v>15.9</v>
+      </c>
+      <c r="J31" s="10">
+        <v>-15.5</v>
       </c>
       <c r="K31" s="9">
-        <v>59.14</v>
-      </c>
-      <c r="L31" s="8">
-        <v>-12</v>
+        <v>70.8</v>
+      </c>
+      <c r="L31" s="10">
+        <v>-12.6</v>
       </c>
       <c r="M31" s="9">
-        <v>10.07</v>
+        <v>11.66</v>
       </c>
       <c r="N31" s="8">
-        <v>-14.6</v>
-      </c>
-      <c r="O31" s="8">
-        <v>-32.799999999999997</v>
+        <v>15.9</v>
+      </c>
+      <c r="O31" s="10">
+        <v>-15.5</v>
       </c>
       <c r="P31" s="9">
-        <v>59.14</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>-12</v>
+        <v>70.8</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>-12.6</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>110</v>
+        <v>127.5</v>
       </c>
       <c r="C32" s="7">
-        <v>130.5</v>
+        <v>141</v>
       </c>
       <c r="D32" s="7">
-        <v>134.5</v>
+        <v>142</v>
       </c>
       <c r="E32" s="7">
-        <v>106.5</v>
-      </c>
-      <c r="F32" s="10">
-        <v>21</v>
-      </c>
-      <c r="G32" s="10">
-        <v>19.18</v>
+        <v>119</v>
+      </c>
+      <c r="F32" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="G32" s="8">
+        <v>8.0500000000000007</v>
       </c>
       <c r="H32" s="9">
-        <v>11.78</v>
-      </c>
-      <c r="I32" s="8">
-        <v>-13.3</v>
-      </c>
-      <c r="J32" s="8">
-        <v>-19.5</v>
+        <v>10.07</v>
+      </c>
+      <c r="I32" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="J32" s="10">
+        <v>-32.799999999999997</v>
       </c>
       <c r="K32" s="9">
-        <v>49.07</v>
-      </c>
-      <c r="L32" s="8">
-        <v>-6.08</v>
+        <v>59.14</v>
+      </c>
+      <c r="L32" s="10">
+        <v>-12</v>
       </c>
       <c r="M32" s="9">
-        <v>11.78</v>
-      </c>
-      <c r="N32" s="8">
-        <v>-13.3</v>
-      </c>
-      <c r="O32" s="8">
-        <v>-19.5</v>
+        <v>10.07</v>
+      </c>
+      <c r="N32" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="O32" s="10">
+        <v>-32.799999999999997</v>
       </c>
       <c r="P32" s="9">
-        <v>49.07</v>
-      </c>
-      <c r="Q32" s="8">
-        <v>-6.08</v>
+        <v>59.14</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>-12</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="C33" s="7">
-        <v>109.5</v>
+        <v>130.5</v>
       </c>
       <c r="D33" s="7">
-        <v>158</v>
+        <v>134.5</v>
       </c>
       <c r="E33" s="7">
-        <v>93.8</v>
+        <v>106.5</v>
       </c>
       <c r="F33" s="8">
-        <v>-46.5</v>
+        <v>21</v>
       </c>
       <c r="G33" s="8">
-        <v>-29.81</v>
+        <v>19.18</v>
       </c>
       <c r="H33" s="9">
-        <v>13.59</v>
+        <v>11.78</v>
       </c>
       <c r="I33" s="10">
-        <v>12.9</v>
-      </c>
-      <c r="J33" s="8">
-        <v>-5.35</v>
+        <v>-13.3</v>
+      </c>
+      <c r="J33" s="10">
+        <v>-19.5</v>
       </c>
       <c r="K33" s="9">
-        <v>37.29</v>
-      </c>
-      <c r="L33" s="8">
-        <v>-0.84</v>
+        <v>49.07</v>
+      </c>
+      <c r="L33" s="10">
+        <v>-6.08</v>
       </c>
       <c r="M33" s="9">
-        <v>13.59</v>
+        <v>11.78</v>
       </c>
       <c r="N33" s="10">
-        <v>12.9</v>
-      </c>
-      <c r="O33" s="8">
-        <v>-5.35</v>
+        <v>-13.3</v>
+      </c>
+      <c r="O33" s="10">
+        <v>-19.5</v>
       </c>
       <c r="P33" s="9">
-        <v>37.29</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>-0.84</v>
+        <v>49.07</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>-6.08</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C34" s="7">
-        <v>156</v>
+        <v>109.5</v>
       </c>
       <c r="D34" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E34" s="7">
-        <v>140</v>
+        <v>93.8</v>
       </c>
       <c r="F34" s="10">
-        <v>11.5</v>
+        <v>-46.5</v>
       </c>
       <c r="G34" s="10">
-        <v>7.96</v>
+        <v>-29.81</v>
       </c>
       <c r="H34" s="9">
-        <v>12.03</v>
-      </c>
-      <c r="I34" s="10">
-        <v>3.15</v>
+        <v>13.59</v>
+      </c>
+      <c r="I34" s="8">
+        <v>12.9</v>
       </c>
       <c r="J34" s="10">
-        <v>25.6</v>
+        <v>-5.35</v>
       </c>
       <c r="K34" s="9">
-        <v>23.7</v>
+        <v>37.29</v>
       </c>
       <c r="L34" s="10">
-        <v>1.93</v>
+        <v>-0.84</v>
       </c>
       <c r="M34" s="9">
-        <v>12.03</v>
-      </c>
-      <c r="N34" s="10">
-        <v>3.15</v>
+        <v>13.59</v>
+      </c>
+      <c r="N34" s="8">
+        <v>12.9</v>
       </c>
       <c r="O34" s="10">
-        <v>25.6</v>
+        <v>-5.35</v>
       </c>
       <c r="P34" s="9">
-        <v>23.7</v>
+        <v>37.29</v>
       </c>
       <c r="Q34" s="10">
-        <v>1.93</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>150.5</v>
+        <v>144</v>
       </c>
       <c r="C35" s="7">
-        <v>144.5</v>
+        <v>156</v>
       </c>
       <c r="D35" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E35" s="7">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F35" s="8">
-        <v>-6</v>
+        <v>11.5</v>
       </c>
       <c r="G35" s="8">
-        <v>-3.99</v>
+        <v>7.96</v>
       </c>
       <c r="H35" s="9">
-        <v>11.67</v>
+        <v>12.03</v>
       </c>
       <c r="I35" s="8">
-        <v>-19.8</v>
+        <v>3.15</v>
       </c>
       <c r="J35" s="8">
-        <v>-14.6</v>
+        <v>25.6</v>
       </c>
       <c r="K35" s="9">
-        <v>11.67</v>
+        <v>23.7</v>
       </c>
       <c r="L35" s="8">
-        <v>-14.6</v>
+        <v>1.93</v>
       </c>
       <c r="M35" s="9">
-        <v>11.67</v>
+        <v>12.03</v>
       </c>
       <c r="N35" s="8">
-        <v>-19.8</v>
+        <v>3.15</v>
       </c>
       <c r="O35" s="8">
-        <v>-14.6</v>
+        <v>25.6</v>
       </c>
       <c r="P35" s="9">
-        <v>11.67</v>
+        <v>23.7</v>
       </c>
       <c r="Q35" s="8">
-        <v>-14.6</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>160</v>
+        <v>150.5</v>
       </c>
       <c r="C36" s="7">
-        <v>150.5</v>
+        <v>144.5</v>
       </c>
       <c r="D36" s="7">
-        <v>160.5</v>
+        <v>154</v>
       </c>
       <c r="E36" s="7">
-        <v>150</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-7.5</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-4.75</v>
+        <v>144</v>
+      </c>
+      <c r="F36" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G36" s="10">
+        <v>-3.99</v>
       </c>
       <c r="H36" s="9">
-        <v>14.49</v>
-      </c>
-      <c r="I36" s="8">
-        <v>-2.94</v>
+        <v>11.67</v>
+      </c>
+      <c r="I36" s="10">
+        <v>-19.8</v>
       </c>
       <c r="J36" s="10">
-        <v>8.75</v>
+        <v>-14.6</v>
       </c>
       <c r="K36" s="9">
-        <v>171.1</v>
+        <v>11.67</v>
       </c>
       <c r="L36" s="10">
-        <v>6.81</v>
+        <v>-14.6</v>
       </c>
       <c r="M36" s="9">
-        <v>14.49</v>
-      </c>
-      <c r="N36" s="8">
-        <v>-2.94</v>
+        <v>11.67</v>
+      </c>
+      <c r="N36" s="10">
+        <v>-19.8</v>
       </c>
       <c r="O36" s="10">
-        <v>8.75</v>
+        <v>-14.6</v>
       </c>
       <c r="P36" s="9">
-        <v>171.1</v>
+        <v>11.67</v>
       </c>
       <c r="Q36" s="10">
-        <v>6.81</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
+        <v>160</v>
+      </c>
+      <c r="C37" s="7">
+        <v>150.5</v>
+      </c>
+      <c r="D37" s="7">
+        <v>160.5</v>
+      </c>
+      <c r="E37" s="7">
         <v>150</v>
       </c>
-      <c r="C37" s="7">
-        <v>158</v>
-      </c>
-      <c r="D37" s="7">
-        <v>164.5</v>
-      </c>
-      <c r="E37" s="7">
-        <v>148</v>
-      </c>
       <c r="F37" s="10">
-        <v>8</v>
+        <v>-7.5</v>
       </c>
       <c r="G37" s="10">
-        <v>5.33</v>
+        <v>-4.75</v>
       </c>
       <c r="H37" s="9">
-        <v>14.93</v>
-      </c>
-      <c r="I37" s="8">
-        <v>-5.63</v>
-      </c>
-      <c r="J37" s="10">
-        <v>3.29</v>
+        <v>14.49</v>
+      </c>
+      <c r="I37" s="10">
+        <v>-2.94</v>
+      </c>
+      <c r="J37" s="8">
+        <v>8.75</v>
       </c>
       <c r="K37" s="9">
-        <v>156.6</v>
-      </c>
-      <c r="L37" s="10">
-        <v>6.64</v>
+        <v>171.1</v>
+      </c>
+      <c r="L37" s="8">
+        <v>6.81</v>
       </c>
       <c r="M37" s="9">
-        <v>14.93</v>
-      </c>
-      <c r="N37" s="8">
-        <v>-5.63</v>
-      </c>
-      <c r="O37" s="10">
-        <v>3.29</v>
+        <v>14.49</v>
+      </c>
+      <c r="N37" s="10">
+        <v>-2.94</v>
+      </c>
+      <c r="O37" s="8">
+        <v>8.75</v>
       </c>
       <c r="P37" s="9">
-        <v>156.6</v>
-      </c>
-      <c r="Q37" s="10">
-        <v>6.64</v>
+        <v>171.1</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>6.81</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="7">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D38" s="7">
-        <v>157.5</v>
+        <v>164.5</v>
       </c>
       <c r="E38" s="7">
-        <v>141.5</v>
+        <v>148</v>
       </c>
       <c r="F38" s="8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G38" s="8">
-        <v>-0.66</v>
+        <v>5.33</v>
       </c>
       <c r="H38" s="9">
-        <v>15.82</v>
+        <v>14.93</v>
       </c>
       <c r="I38" s="10">
-        <v>4.68</v>
-      </c>
-      <c r="J38" s="10">
-        <v>6.58</v>
+        <v>-5.63</v>
+      </c>
+      <c r="J38" s="8">
+        <v>3.29</v>
       </c>
       <c r="K38" s="9">
-        <v>141.69999999999999</v>
-      </c>
-      <c r="L38" s="10">
-        <v>7</v>
+        <v>156.6</v>
+      </c>
+      <c r="L38" s="8">
+        <v>6.64</v>
       </c>
       <c r="M38" s="9">
-        <v>15.82</v>
+        <v>14.93</v>
       </c>
       <c r="N38" s="10">
-        <v>4.68</v>
-      </c>
-      <c r="O38" s="10">
-        <v>6.58</v>
+        <v>-5.63</v>
+      </c>
+      <c r="O38" s="8">
+        <v>3.29</v>
       </c>
       <c r="P38" s="9">
-        <v>141.69999999999999</v>
-      </c>
-      <c r="Q38" s="10">
-        <v>7</v>
+        <v>156.6</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>6.64</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C39" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D39" s="7">
-        <v>167</v>
+        <v>157.5</v>
       </c>
       <c r="E39" s="7">
-        <v>150.5</v>
-      </c>
-      <c r="F39" s="8">
-        <v>-12</v>
-      </c>
-      <c r="G39" s="8">
-        <v>-7.36</v>
+        <v>141.5</v>
+      </c>
+      <c r="F39" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G39" s="10">
+        <v>-0.66</v>
       </c>
       <c r="H39" s="9">
-        <v>15.11</v>
-      </c>
-      <c r="I39" s="10">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="J39" s="10">
-        <v>15.3</v>
+        <v>15.82</v>
+      </c>
+      <c r="I39" s="8">
+        <v>4.68</v>
+      </c>
+      <c r="J39" s="8">
+        <v>6.58</v>
       </c>
       <c r="K39" s="9">
-        <v>125.9</v>
-      </c>
-      <c r="L39" s="10">
-        <v>7.05</v>
+        <v>141.69999999999999</v>
+      </c>
+      <c r="L39" s="8">
+        <v>7</v>
       </c>
       <c r="M39" s="9">
-        <v>15.11</v>
-      </c>
-      <c r="N39" s="10">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="O39" s="10">
-        <v>15.3</v>
+        <v>15.82</v>
+      </c>
+      <c r="N39" s="8">
+        <v>4.68</v>
+      </c>
+      <c r="O39" s="8">
+        <v>6.58</v>
       </c>
       <c r="P39" s="9">
-        <v>125.9</v>
-      </c>
-      <c r="Q39" s="10">
-        <v>7.05</v>
+        <v>141.69999999999999</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>172.5</v>
+        <v>163</v>
       </c>
       <c r="C40" s="7">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D40" s="7">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E40" s="7">
-        <v>160</v>
-      </c>
-      <c r="F40" s="8">
-        <v>-11.5</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-6.59</v>
+        <v>150.5</v>
+      </c>
+      <c r="F40" s="10">
+        <v>-12</v>
+      </c>
+      <c r="G40" s="10">
+        <v>-7.36</v>
       </c>
       <c r="H40" s="9">
-        <v>14.79</v>
+        <v>15.11</v>
       </c>
       <c r="I40" s="8">
-        <v>-1.08</v>
-      </c>
-      <c r="J40" s="10">
-        <v>3.15</v>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="J40" s="8">
+        <v>15.3</v>
       </c>
       <c r="K40" s="9">
-        <v>110.8</v>
-      </c>
-      <c r="L40" s="10">
-        <v>6.01</v>
+        <v>125.9</v>
+      </c>
+      <c r="L40" s="8">
+        <v>7.05</v>
       </c>
       <c r="M40" s="9">
-        <v>14.79</v>
+        <v>15.11</v>
       </c>
       <c r="N40" s="8">
-        <v>-1.08</v>
-      </c>
-      <c r="O40" s="10">
-        <v>3.15</v>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="O40" s="8">
+        <v>15.3</v>
       </c>
       <c r="P40" s="9">
-        <v>110.8</v>
-      </c>
-      <c r="Q40" s="10">
-        <v>6.01</v>
+        <v>125.9</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>7.05</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>157.5</v>
+        <v>172.5</v>
       </c>
       <c r="C41" s="7">
-        <v>174.5</v>
+        <v>163</v>
       </c>
       <c r="D41" s="7">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E41" s="7">
-        <v>157.5</v>
+        <v>160</v>
       </c>
       <c r="F41" s="10">
-        <v>19</v>
+        <v>-11.5</v>
       </c>
       <c r="G41" s="10">
-        <v>12.22</v>
+        <v>-6.59</v>
       </c>
       <c r="H41" s="9">
-        <v>14.95</v>
+        <v>14.79</v>
       </c>
       <c r="I41" s="10">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="J41" s="10">
-        <v>4.1500000000000004</v>
+        <v>-1.08</v>
+      </c>
+      <c r="J41" s="8">
+        <v>3.15</v>
       </c>
       <c r="K41" s="9">
-        <v>95.99</v>
-      </c>
-      <c r="L41" s="10">
-        <v>6.47</v>
+        <v>110.8</v>
+      </c>
+      <c r="L41" s="8">
+        <v>6.01</v>
       </c>
       <c r="M41" s="9">
-        <v>14.95</v>
+        <v>14.79</v>
       </c>
       <c r="N41" s="10">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="O41" s="10">
-        <v>4.1500000000000004</v>
+        <v>-1.08</v>
+      </c>
+      <c r="O41" s="8">
+        <v>3.15</v>
       </c>
       <c r="P41" s="9">
-        <v>95.99</v>
-      </c>
-      <c r="Q41" s="10">
-        <v>6.47</v>
+        <v>110.8</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>6.01</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>157</v>
+        <v>157.5</v>
       </c>
       <c r="C42" s="7">
-        <v>155.5</v>
+        <v>174.5</v>
       </c>
       <c r="D42" s="7">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E42" s="7">
-        <v>155.5</v>
+        <v>157.5</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8">
-        <v>-1.89</v>
+        <v>12.22</v>
       </c>
       <c r="H42" s="9">
-        <v>13.8</v>
+        <v>14.95</v>
       </c>
       <c r="I42" s="8">
-        <v>-7.88</v>
-      </c>
-      <c r="J42" s="10">
-        <v>4.62</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="J42" s="8">
+        <v>4.1500000000000004</v>
       </c>
       <c r="K42" s="9">
-        <v>81.040000000000006</v>
-      </c>
-      <c r="L42" s="10">
-        <v>6.91</v>
+        <v>95.99</v>
+      </c>
+      <c r="L42" s="8">
+        <v>6.47</v>
       </c>
       <c r="M42" s="9">
-        <v>13.8</v>
+        <v>14.95</v>
       </c>
       <c r="N42" s="8">
-        <v>-7.88</v>
-      </c>
-      <c r="O42" s="10">
-        <v>4.62</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O42" s="8">
+        <v>4.1500000000000004</v>
       </c>
       <c r="P42" s="9">
-        <v>81.040000000000006</v>
-      </c>
-      <c r="Q42" s="10">
-        <v>6.91</v>
+        <v>95.99</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>6.47</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C43" s="7">
-        <v>158.5</v>
+        <v>155.5</v>
       </c>
       <c r="D43" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E43" s="7">
-        <v>147</v>
+        <v>155.5</v>
       </c>
       <c r="F43" s="10">
-        <v>6.5</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="10">
-        <v>4.28</v>
+        <v>-1.89</v>
       </c>
       <c r="H43" s="9">
-        <v>14.98</v>
+        <v>13.8</v>
       </c>
       <c r="I43" s="10">
-        <v>2.35</v>
-      </c>
-      <c r="J43" s="10">
-        <v>4.1399999999999997</v>
+        <v>-7.88</v>
+      </c>
+      <c r="J43" s="8">
+        <v>4.62</v>
       </c>
       <c r="K43" s="9">
-        <v>67.239999999999995</v>
-      </c>
-      <c r="L43" s="10">
-        <v>7.39</v>
+        <v>81.040000000000006</v>
+      </c>
+      <c r="L43" s="8">
+        <v>6.91</v>
       </c>
       <c r="M43" s="9">
-        <v>14.98</v>
+        <v>13.8</v>
       </c>
       <c r="N43" s="10">
-        <v>2.35</v>
-      </c>
-      <c r="O43" s="10">
-        <v>4.1399999999999997</v>
+        <v>-7.88</v>
+      </c>
+      <c r="O43" s="8">
+        <v>4.62</v>
       </c>
       <c r="P43" s="9">
-        <v>67.239999999999995</v>
-      </c>
-      <c r="Q43" s="10">
-        <v>7.39</v>
+        <v>81.040000000000006</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>6.91</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>147.5</v>
+        <v>150</v>
       </c>
       <c r="C44" s="7">
-        <v>152</v>
+        <v>158.5</v>
       </c>
       <c r="D44" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E44" s="7">
-        <v>143</v>
-      </c>
-      <c r="F44" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="G44" s="10">
-        <v>3.05</v>
+        <v>147</v>
+      </c>
+      <c r="F44" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="G44" s="8">
+        <v>4.28</v>
       </c>
       <c r="H44" s="9">
-        <v>14.64</v>
-      </c>
-      <c r="I44" s="10">
-        <v>1.94</v>
-      </c>
-      <c r="J44" s="10">
-        <v>11.3</v>
+        <v>14.98</v>
+      </c>
+      <c r="I44" s="8">
+        <v>2.35</v>
+      </c>
+      <c r="J44" s="8">
+        <v>4.1399999999999997</v>
       </c>
       <c r="K44" s="9">
-        <v>52.25</v>
-      </c>
-      <c r="L44" s="10">
-        <v>8.36</v>
+        <v>67.239999999999995</v>
+      </c>
+      <c r="L44" s="8">
+        <v>7.39</v>
       </c>
       <c r="M44" s="9">
-        <v>14.64</v>
-      </c>
-      <c r="N44" s="10">
-        <v>1.94</v>
-      </c>
-      <c r="O44" s="10">
-        <v>11.3</v>
+        <v>14.98</v>
+      </c>
+      <c r="N44" s="8">
+        <v>2.35</v>
+      </c>
+      <c r="O44" s="8">
+        <v>4.1399999999999997</v>
       </c>
       <c r="P44" s="9">
-        <v>52.25</v>
-      </c>
-      <c r="Q44" s="10">
-        <v>8.36</v>
+        <v>67.239999999999995</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>7.39</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>125.5</v>
+        <v>147.5</v>
       </c>
       <c r="C45" s="7">
-        <v>147.5</v>
+        <v>152</v>
       </c>
       <c r="D45" s="7">
-        <v>150.5</v>
+        <v>170</v>
       </c>
       <c r="E45" s="7">
-        <v>125</v>
-      </c>
-      <c r="F45" s="10">
-        <v>22</v>
-      </c>
-      <c r="G45" s="10">
-        <v>17.53</v>
+        <v>143</v>
+      </c>
+      <c r="F45" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G45" s="8">
+        <v>3.05</v>
       </c>
       <c r="H45" s="9">
-        <v>14.36</v>
-      </c>
-      <c r="I45" s="10">
-        <v>49.9</v>
-      </c>
-      <c r="J45" s="10">
-        <v>7.48</v>
+        <v>14.64</v>
+      </c>
+      <c r="I45" s="8">
+        <v>1.94</v>
+      </c>
+      <c r="J45" s="8">
+        <v>11.3</v>
       </c>
       <c r="K45" s="9">
-        <v>37.61</v>
-      </c>
-      <c r="L45" s="10">
-        <v>7.25</v>
+        <v>52.25</v>
+      </c>
+      <c r="L45" s="8">
+        <v>8.36</v>
       </c>
       <c r="M45" s="9">
-        <v>14.36</v>
-      </c>
-      <c r="N45" s="10">
-        <v>49.9</v>
-      </c>
-      <c r="O45" s="10">
-        <v>7.48</v>
+        <v>14.64</v>
+      </c>
+      <c r="N45" s="8">
+        <v>1.94</v>
+      </c>
+      <c r="O45" s="8">
+        <v>11.3</v>
       </c>
       <c r="P45" s="9">
-        <v>37.61</v>
-      </c>
-      <c r="Q45" s="10">
-        <v>7.25</v>
+        <v>52.25</v>
+      </c>
+      <c r="Q45" s="8">
+        <v>8.36</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>117</v>
+        <v>125.5</v>
       </c>
       <c r="C46" s="7">
-        <v>125.5</v>
+        <v>147.5</v>
       </c>
       <c r="D46" s="7">
-        <v>135</v>
+        <v>150.5</v>
       </c>
       <c r="E46" s="7">
-        <v>115.5</v>
-      </c>
-      <c r="F46" s="10">
-        <v>10</v>
-      </c>
-      <c r="G46" s="10">
-        <v>8.66</v>
+        <v>125</v>
+      </c>
+      <c r="F46" s="8">
+        <v>22</v>
+      </c>
+      <c r="G46" s="8">
+        <v>17.53</v>
       </c>
       <c r="H46" s="9">
-        <v>9.58</v>
+        <v>14.36</v>
       </c>
       <c r="I46" s="8">
-        <v>-29.9</v>
-      </c>
-      <c r="J46" s="10">
-        <v>19.399999999999999</v>
+        <v>49.9</v>
+      </c>
+      <c r="J46" s="8">
+        <v>7.48</v>
       </c>
       <c r="K46" s="9">
-        <v>23.25</v>
-      </c>
-      <c r="L46" s="10">
-        <v>7.11</v>
+        <v>37.61</v>
+      </c>
+      <c r="L46" s="8">
+        <v>7.25</v>
       </c>
       <c r="M46" s="9">
-        <v>9.58</v>
+        <v>14.36</v>
       </c>
       <c r="N46" s="8">
-        <v>-29.9</v>
-      </c>
-      <c r="O46" s="10">
-        <v>19.399999999999999</v>
+        <v>49.9</v>
+      </c>
+      <c r="O46" s="8">
+        <v>7.48</v>
       </c>
       <c r="P46" s="9">
-        <v>23.25</v>
-      </c>
-      <c r="Q46" s="10">
-        <v>7.11</v>
+        <v>37.61</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>7.25</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C47" s="7">
+        <v>125.5</v>
+      </c>
+      <c r="D47" s="7">
+        <v>135</v>
+      </c>
+      <c r="E47" s="7">
         <v>115.5</v>
       </c>
-      <c r="D47" s="7">
-        <v>117</v>
-      </c>
-      <c r="E47" s="7">
-        <v>105</v>
-      </c>
-      <c r="F47" s="10">
-        <v>3</v>
-      </c>
-      <c r="G47" s="10">
-        <v>2.67</v>
+      <c r="F47" s="8">
+        <v>10</v>
+      </c>
+      <c r="G47" s="8">
+        <v>8.66</v>
       </c>
       <c r="H47" s="9">
-        <v>13.67</v>
+        <v>9.58</v>
       </c>
       <c r="I47" s="10">
-        <v>1.86</v>
+        <v>-29.9</v>
       </c>
       <c r="J47" s="8">
-        <v>-0.08</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="K47" s="9">
-        <v>13.67</v>
+        <v>23.25</v>
       </c>
       <c r="L47" s="8">
-        <v>-0.08</v>
+        <v>7.11</v>
       </c>
       <c r="M47" s="9">
-        <v>13.67</v>
+        <v>9.58</v>
       </c>
       <c r="N47" s="10">
-        <v>1.86</v>
+        <v>-29.9</v>
       </c>
       <c r="O47" s="8">
-        <v>-0.08</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="P47" s="9">
-        <v>13.67</v>
+        <v>23.25</v>
       </c>
       <c r="Q47" s="8">
-        <v>-0.08</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="C48" s="7">
-        <v>112.5</v>
+        <v>115.5</v>
       </c>
       <c r="D48" s="7">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E48" s="7">
-        <v>104</v>
-      </c>
-      <c r="F48" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G48" s="10">
-        <v>0.45</v>
+        <v>105</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3</v>
+      </c>
+      <c r="G48" s="8">
+        <v>2.67</v>
       </c>
       <c r="H48" s="9">
-        <v>13.33</v>
+        <v>13.67</v>
       </c>
       <c r="I48" s="8">
-        <v>-7.81</v>
+        <v>1.86</v>
       </c>
       <c r="J48" s="10">
-        <v>6.51</v>
+        <v>-0.08</v>
       </c>
       <c r="K48" s="9">
-        <v>160.19999999999999</v>
+        <v>13.67</v>
       </c>
       <c r="L48" s="10">
-        <v>9.6300000000000008</v>
+        <v>-0.08</v>
       </c>
       <c r="M48" s="9">
-        <v>13.33</v>
+        <v>13.67</v>
       </c>
       <c r="N48" s="8">
-        <v>-7.81</v>
+        <v>1.86</v>
       </c>
       <c r="O48" s="10">
-        <v>6.51</v>
+        <v>-0.08</v>
       </c>
       <c r="P48" s="9">
-        <v>160.19999999999999</v>
+        <v>13.67</v>
       </c>
       <c r="Q48" s="10">
-        <v>9.6300000000000008</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>88</v>
+        <v>113.5</v>
       </c>
       <c r="C49" s="7">
-        <v>112</v>
+        <v>112.5</v>
       </c>
       <c r="D49" s="7">
-        <v>114.5</v>
+        <v>124</v>
       </c>
       <c r="E49" s="7">
-        <v>87</v>
-      </c>
-      <c r="F49" s="10">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="G49" s="10">
-        <v>45.83</v>
+        <v>104</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0.45</v>
       </c>
       <c r="H49" s="9">
-        <v>14.46</v>
-      </c>
-      <c r="I49" s="8">
-        <v>-2.62</v>
-      </c>
-      <c r="J49" s="10">
-        <v>7.7</v>
+        <v>13.33</v>
+      </c>
+      <c r="I49" s="10">
+        <v>-7.81</v>
+      </c>
+      <c r="J49" s="8">
+        <v>6.51</v>
       </c>
       <c r="K49" s="9">
-        <v>146.9</v>
-      </c>
-      <c r="L49" s="10">
-        <v>9.92</v>
+        <v>160.19999999999999</v>
+      </c>
+      <c r="L49" s="8">
+        <v>9.6300000000000008</v>
       </c>
       <c r="M49" s="9">
-        <v>14.46</v>
-      </c>
-      <c r="N49" s="8">
-        <v>-2.62</v>
-      </c>
-      <c r="O49" s="10">
-        <v>7.7</v>
+        <v>13.33</v>
+      </c>
+      <c r="N49" s="10">
+        <v>-7.81</v>
+      </c>
+      <c r="O49" s="8">
+        <v>6.51</v>
       </c>
       <c r="P49" s="9">
-        <v>146.9</v>
-      </c>
-      <c r="Q49" s="10">
-        <v>9.92</v>
+        <v>160.19999999999999</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>9.6300000000000008</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>17</v>
+        <v>43405</v>
+      </c>
+      <c r="B50" s="7">
+        <v>88</v>
+      </c>
+      <c r="C50" s="7">
+        <v>112</v>
+      </c>
+      <c r="D50" s="7">
+        <v>114.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>87</v>
+      </c>
+      <c r="F50" s="8">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="G50" s="8">
+        <v>45.83</v>
       </c>
       <c r="H50" s="9">
-        <v>14.85</v>
+        <v>14.46</v>
       </c>
       <c r="I50" s="10">
-        <v>13.2</v>
-      </c>
-      <c r="J50" s="10">
-        <v>19.7</v>
+        <v>-2.62</v>
+      </c>
+      <c r="J50" s="8">
+        <v>7.7</v>
       </c>
       <c r="K50" s="9">
-        <v>132.4</v>
-      </c>
-      <c r="L50" s="10">
-        <v>10.199999999999999</v>
+        <v>146.9</v>
+      </c>
+      <c r="L50" s="8">
+        <v>9.92</v>
       </c>
       <c r="M50" s="9">
-        <v>14.85</v>
+        <v>14.46</v>
       </c>
       <c r="N50" s="10">
-        <v>13.2</v>
-      </c>
-      <c r="O50" s="10">
-        <v>19.7</v>
+        <v>-2.62</v>
+      </c>
+      <c r="O50" s="8">
+        <v>7.7</v>
       </c>
       <c r="P50" s="9">
-        <v>132.4</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>10.199999999999999</v>
+        <v>146.9</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>9.92</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3844,39 +3852,39 @@
         <v>17</v>
       </c>
       <c r="H51" s="9">
-        <v>13.11</v>
+        <v>14.85</v>
       </c>
       <c r="I51" s="8">
-        <v>-8.5500000000000007</v>
+        <v>13.2</v>
       </c>
       <c r="J51" s="8">
-        <v>-3.76</v>
+        <v>19.7</v>
       </c>
       <c r="K51" s="9">
-        <v>117.6</v>
-      </c>
-      <c r="L51" s="10">
-        <v>9.06</v>
+        <v>132.4</v>
+      </c>
+      <c r="L51" s="8">
+        <v>10.199999999999999</v>
       </c>
       <c r="M51" s="9">
-        <v>13.11</v>
+        <v>14.85</v>
       </c>
       <c r="N51" s="8">
-        <v>-8.5500000000000007</v>
+        <v>13.2</v>
       </c>
       <c r="O51" s="8">
-        <v>-3.76</v>
+        <v>19.7</v>
       </c>
       <c r="P51" s="9">
-        <v>117.6</v>
-      </c>
-      <c r="Q51" s="10">
-        <v>9.06</v>
+        <v>132.4</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3897,39 +3905,39 @@
         <v>17</v>
       </c>
       <c r="H52" s="9">
-        <v>14.33</v>
-      </c>
-      <c r="I52" s="8">
-        <v>-0.11</v>
+        <v>13.11</v>
+      </c>
+      <c r="I52" s="10">
+        <v>-8.5500000000000007</v>
       </c>
       <c r="J52" s="10">
-        <v>10.4</v>
+        <v>-3.76</v>
       </c>
       <c r="K52" s="9">
-        <v>104.5</v>
-      </c>
-      <c r="L52" s="10">
-        <v>10.9</v>
+        <v>117.6</v>
+      </c>
+      <c r="L52" s="8">
+        <v>9.06</v>
       </c>
       <c r="M52" s="9">
-        <v>14.33</v>
-      </c>
-      <c r="N52" s="8">
-        <v>-0.11</v>
+        <v>13.11</v>
+      </c>
+      <c r="N52" s="10">
+        <v>-8.5500000000000007</v>
       </c>
       <c r="O52" s="10">
-        <v>10.4</v>
+        <v>-3.76</v>
       </c>
       <c r="P52" s="9">
-        <v>104.5</v>
-      </c>
-      <c r="Q52" s="10">
-        <v>10.9</v>
+        <v>117.6</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>9.06</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3950,39 +3958,39 @@
         <v>17</v>
       </c>
       <c r="H53" s="9">
-        <v>14.35</v>
+        <v>14.33</v>
       </c>
       <c r="I53" s="10">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="J53" s="10">
-        <v>16.2</v>
+        <v>-0.11</v>
+      </c>
+      <c r="J53" s="8">
+        <v>10.4</v>
       </c>
       <c r="K53" s="9">
-        <v>90.15</v>
-      </c>
-      <c r="L53" s="10">
-        <v>11</v>
+        <v>104.5</v>
+      </c>
+      <c r="L53" s="8">
+        <v>10.9</v>
       </c>
       <c r="M53" s="9">
-        <v>14.35</v>
+        <v>14.33</v>
       </c>
       <c r="N53" s="10">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="O53" s="10">
-        <v>16.2</v>
+        <v>-0.11</v>
+      </c>
+      <c r="O53" s="8">
+        <v>10.4</v>
       </c>
       <c r="P53" s="9">
-        <v>90.15</v>
-      </c>
-      <c r="Q53" s="10">
-        <v>11</v>
+        <v>104.5</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>10.9</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4003,39 +4011,39 @@
         <v>17</v>
       </c>
       <c r="H54" s="9">
-        <v>13.19</v>
+        <v>14.35</v>
       </c>
       <c r="I54" s="8">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="J54" s="10">
-        <v>7.83</v>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="J54" s="8">
+        <v>16.2</v>
       </c>
       <c r="K54" s="9">
-        <v>75.8</v>
-      </c>
-      <c r="L54" s="10">
-        <v>10.1</v>
+        <v>90.15</v>
+      </c>
+      <c r="L54" s="8">
+        <v>11</v>
       </c>
       <c r="M54" s="9">
-        <v>13.19</v>
+        <v>14.35</v>
       </c>
       <c r="N54" s="8">
-        <v>-8.3000000000000007</v>
-      </c>
-      <c r="O54" s="10">
-        <v>7.83</v>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="O54" s="8">
+        <v>16.2</v>
       </c>
       <c r="P54" s="9">
-        <v>75.8</v>
-      </c>
-      <c r="Q54" s="10">
-        <v>10.1</v>
+        <v>90.15</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4056,39 +4064,39 @@
         <v>17</v>
       </c>
       <c r="H55" s="9">
-        <v>14.39</v>
+        <v>13.19</v>
       </c>
       <c r="I55" s="10">
-        <v>9.39</v>
-      </c>
-      <c r="J55" s="10">
-        <v>16.5</v>
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="J55" s="8">
+        <v>7.83</v>
       </c>
       <c r="K55" s="9">
-        <v>62.61</v>
-      </c>
-      <c r="L55" s="10">
-        <v>10.6</v>
+        <v>75.8</v>
+      </c>
+      <c r="L55" s="8">
+        <v>10.1</v>
       </c>
       <c r="M55" s="9">
-        <v>14.39</v>
-      </c>
-      <c r="N55" s="8">
-        <v>-1.96</v>
-      </c>
-      <c r="O55" s="10">
-        <v>16.5</v>
+        <v>13.19</v>
+      </c>
+      <c r="N55" s="10">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="O55" s="8">
+        <v>7.83</v>
       </c>
       <c r="P55" s="9">
-        <v>62.61</v>
-      </c>
-      <c r="Q55" s="10">
-        <v>10.6</v>
+        <v>75.8</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>10.1</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4109,39 +4117,39 @@
         <v>17</v>
       </c>
       <c r="H56" s="9">
-        <v>13.15</v>
+        <v>14.39</v>
       </c>
       <c r="I56" s="8">
-        <v>-8.43</v>
-      </c>
-      <c r="J56" s="10">
-        <v>10.9</v>
+        <v>9.39</v>
+      </c>
+      <c r="J56" s="8">
+        <v>16.5</v>
       </c>
       <c r="K56" s="9">
-        <v>48.22</v>
-      </c>
-      <c r="L56" s="10">
-        <v>8.89</v>
+        <v>62.61</v>
+      </c>
+      <c r="L56" s="8">
+        <v>10.6</v>
       </c>
       <c r="M56" s="9">
-        <v>13.15</v>
-      </c>
-      <c r="N56" s="8">
-        <v>-8.43</v>
-      </c>
-      <c r="O56" s="10">
-        <v>10.9</v>
+        <v>14.39</v>
+      </c>
+      <c r="N56" s="10">
+        <v>-1.96</v>
+      </c>
+      <c r="O56" s="8">
+        <v>16.5</v>
       </c>
       <c r="P56" s="9">
-        <v>48.22</v>
-      </c>
-      <c r="Q56" s="10">
-        <v>8.89</v>
+        <v>62.61</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>10.6</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4162,39 +4170,39 @@
         <v>17</v>
       </c>
       <c r="H57" s="9">
-        <v>13.36</v>
+        <v>13.15</v>
       </c>
       <c r="I57" s="10">
-        <v>50</v>
-      </c>
-      <c r="J57" s="10">
-        <v>4.83</v>
+        <v>-8.43</v>
+      </c>
+      <c r="J57" s="8">
+        <v>10.9</v>
       </c>
       <c r="K57" s="9">
-        <v>35.07</v>
-      </c>
-      <c r="L57" s="10">
-        <v>8.14</v>
+        <v>48.22</v>
+      </c>
+      <c r="L57" s="8">
+        <v>8.89</v>
       </c>
       <c r="M57" s="9">
-        <v>13.36</v>
+        <v>13.15</v>
       </c>
       <c r="N57" s="10">
-        <v>50</v>
-      </c>
-      <c r="O57" s="10">
-        <v>4.83</v>
+        <v>-8.43</v>
+      </c>
+      <c r="O57" s="8">
+        <v>10.9</v>
       </c>
       <c r="P57" s="9">
-        <v>35.07</v>
-      </c>
-      <c r="Q57" s="10">
-        <v>8.14</v>
+        <v>48.22</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>8.89</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4215,39 +4223,39 @@
         <v>17</v>
       </c>
       <c r="H58" s="9">
-        <v>8.0299999999999994</v>
+        <v>13.36</v>
       </c>
       <c r="I58" s="8">
-        <v>-41.3</v>
+        <v>50</v>
       </c>
       <c r="J58" s="8">
-        <v>-12.1</v>
+        <v>4.83</v>
       </c>
       <c r="K58" s="9">
-        <v>21.71</v>
-      </c>
-      <c r="L58" s="10">
-        <v>10.3</v>
+        <v>35.07</v>
+      </c>
+      <c r="L58" s="8">
+        <v>8.14</v>
       </c>
       <c r="M58" s="9">
-        <v>8.0299999999999994</v>
+        <v>13.36</v>
       </c>
       <c r="N58" s="8">
-        <v>-41.3</v>
+        <v>50</v>
       </c>
       <c r="O58" s="8">
-        <v>-12.1</v>
+        <v>4.83</v>
       </c>
       <c r="P58" s="9">
-        <v>21.71</v>
-      </c>
-      <c r="Q58" s="10">
-        <v>10.3</v>
+        <v>35.07</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>8.14</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4268,39 +4276,39 @@
         <v>17</v>
       </c>
       <c r="H59" s="9">
-        <v>13.68</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="I59" s="10">
-        <v>7.41</v>
+        <v>-41.3</v>
       </c>
       <c r="J59" s="10">
-        <v>29.6</v>
+        <v>-12.1</v>
       </c>
       <c r="K59" s="9">
-        <v>13.68</v>
-      </c>
-      <c r="L59" s="10">
-        <v>29.6</v>
+        <v>21.71</v>
+      </c>
+      <c r="L59" s="8">
+        <v>10.3</v>
       </c>
       <c r="M59" s="9">
-        <v>13.68</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="N59" s="10">
-        <v>7.41</v>
+        <v>-41.3</v>
       </c>
       <c r="O59" s="10">
-        <v>29.6</v>
+        <v>-12.1</v>
       </c>
       <c r="P59" s="9">
-        <v>13.68</v>
-      </c>
-      <c r="Q59" s="10">
-        <v>29.6</v>
+        <v>21.71</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>10.3</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4321,39 +4329,39 @@
         <v>17</v>
       </c>
       <c r="H60" s="9">
-        <v>12.51</v>
+        <v>13.68</v>
       </c>
       <c r="I60" s="8">
-        <v>-7.61</v>
+        <v>7.41</v>
       </c>
       <c r="J60" s="8">
-        <v>-0.11</v>
+        <v>29.6</v>
       </c>
       <c r="K60" s="9">
-        <v>146.19999999999999</v>
-      </c>
-      <c r="L60" s="10">
-        <v>0.25</v>
+        <v>13.68</v>
+      </c>
+      <c r="L60" s="8">
+        <v>29.6</v>
       </c>
       <c r="M60" s="9">
-        <v>12.51</v>
+        <v>13.68</v>
       </c>
       <c r="N60" s="8">
-        <v>-7.61</v>
+        <v>7.41</v>
       </c>
       <c r="O60" s="8">
-        <v>-0.11</v>
+        <v>29.6</v>
       </c>
       <c r="P60" s="9">
-        <v>146.19999999999999</v>
-      </c>
-      <c r="Q60" s="10">
-        <v>0.25</v>
+        <v>13.68</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>29.6</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4374,39 +4382,39 @@
         <v>17</v>
       </c>
       <c r="H61" s="9">
-        <v>13.42</v>
+        <v>12.51</v>
       </c>
       <c r="I61" s="10">
-        <v>7.35</v>
+        <v>-7.61</v>
       </c>
       <c r="J61" s="10">
-        <v>4.1399999999999997</v>
+        <v>-0.11</v>
       </c>
       <c r="K61" s="9">
-        <v>133.6</v>
-      </c>
-      <c r="L61" s="10">
-        <v>0.28000000000000003</v>
+        <v>146.19999999999999</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0.25</v>
       </c>
       <c r="M61" s="9">
-        <v>13.42</v>
+        <v>12.51</v>
       </c>
       <c r="N61" s="10">
-        <v>7.35</v>
+        <v>-7.61</v>
       </c>
       <c r="O61" s="10">
-        <v>4.1399999999999997</v>
+        <v>-0.11</v>
       </c>
       <c r="P61" s="9">
-        <v>133.6</v>
-      </c>
-      <c r="Q61" s="10">
-        <v>0.28000000000000003</v>
+        <v>146.19999999999999</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4427,39 +4435,39 @@
         <v>17</v>
       </c>
       <c r="H62" s="9">
-        <v>12.4</v>
+        <v>13.42</v>
       </c>
       <c r="I62" s="8">
-        <v>-9.75</v>
-      </c>
-      <c r="J62" s="10">
-        <v>2.1800000000000002</v>
+        <v>7.35</v>
+      </c>
+      <c r="J62" s="8">
+        <v>4.1399999999999997</v>
       </c>
       <c r="K62" s="9">
-        <v>120.2</v>
+        <v>133.6</v>
       </c>
       <c r="L62" s="8">
-        <v>-0.13</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M62" s="9">
-        <v>12.4</v>
+        <v>13.42</v>
       </c>
       <c r="N62" s="8">
-        <v>-9.75</v>
-      </c>
-      <c r="O62" s="10">
-        <v>2.1800000000000002</v>
+        <v>7.35</v>
+      </c>
+      <c r="O62" s="8">
+        <v>4.1399999999999997</v>
       </c>
       <c r="P62" s="9">
-        <v>120.2</v>
+        <v>133.6</v>
       </c>
       <c r="Q62" s="8">
-        <v>-0.13</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4480,39 +4488,39 @@
         <v>17</v>
       </c>
       <c r="H63" s="9">
-        <v>13.62</v>
+        <v>12.4</v>
       </c>
       <c r="I63" s="10">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="J63" s="10">
-        <v>11.3</v>
+        <v>-9.75</v>
+      </c>
+      <c r="J63" s="8">
+        <v>2.1800000000000002</v>
       </c>
       <c r="K63" s="9">
-        <v>107.8</v>
-      </c>
-      <c r="L63" s="8">
-        <v>-0.39</v>
+        <v>120.2</v>
+      </c>
+      <c r="L63" s="10">
+        <v>-0.13</v>
       </c>
       <c r="M63" s="9">
-        <v>13.62</v>
+        <v>12.4</v>
       </c>
       <c r="N63" s="10">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="O63" s="10">
-        <v>11.3</v>
+        <v>-9.75</v>
+      </c>
+      <c r="O63" s="8">
+        <v>2.1800000000000002</v>
       </c>
       <c r="P63" s="9">
-        <v>107.8</v>
-      </c>
-      <c r="Q63" s="8">
-        <v>-0.39</v>
+        <v>120.2</v>
+      </c>
+      <c r="Q63" s="10">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4533,39 +4541,39 @@
         <v>17</v>
       </c>
       <c r="H64" s="9">
-        <v>12.98</v>
-      </c>
-      <c r="I64" s="10">
-        <v>4.47</v>
-      </c>
-      <c r="J64" s="10">
-        <v>4.79</v>
+        <v>13.62</v>
+      </c>
+      <c r="I64" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="J64" s="8">
+        <v>11.3</v>
       </c>
       <c r="K64" s="9">
-        <v>94.2</v>
-      </c>
-      <c r="L64" s="8">
-        <v>-1.88</v>
+        <v>107.8</v>
+      </c>
+      <c r="L64" s="10">
+        <v>-0.39</v>
       </c>
       <c r="M64" s="9">
-        <v>12.98</v>
-      </c>
-      <c r="N64" s="10">
-        <v>4.47</v>
-      </c>
-      <c r="O64" s="10">
-        <v>4.79</v>
+        <v>13.62</v>
+      </c>
+      <c r="N64" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="O64" s="8">
+        <v>11.3</v>
       </c>
       <c r="P64" s="9">
-        <v>94.2</v>
-      </c>
-      <c r="Q64" s="8">
-        <v>-1.88</v>
+        <v>107.8</v>
+      </c>
+      <c r="Q64" s="10">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4586,39 +4594,39 @@
         <v>17</v>
       </c>
       <c r="H65" s="9">
-        <v>12.36</v>
+        <v>12.98</v>
       </c>
       <c r="I65" s="8">
-        <v>-0.53</v>
-      </c>
-      <c r="J65" s="10">
-        <v>7.65</v>
+        <v>4.47</v>
+      </c>
+      <c r="J65" s="8">
+        <v>4.79</v>
       </c>
       <c r="K65" s="9">
-        <v>81.22</v>
-      </c>
-      <c r="L65" s="8">
-        <v>-2.87</v>
+        <v>94.2</v>
+      </c>
+      <c r="L65" s="10">
+        <v>-1.88</v>
       </c>
       <c r="M65" s="9">
-        <v>12.36</v>
+        <v>12.98</v>
       </c>
       <c r="N65" s="8">
-        <v>-0.53</v>
-      </c>
-      <c r="O65" s="10">
-        <v>7.65</v>
+        <v>4.47</v>
+      </c>
+      <c r="O65" s="8">
+        <v>4.79</v>
       </c>
       <c r="P65" s="9">
-        <v>81.22</v>
-      </c>
-      <c r="Q65" s="8">
-        <v>-2.87</v>
+        <v>94.2</v>
+      </c>
+      <c r="Q65" s="10">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4639,86 +4647,139 @@
         <v>17</v>
       </c>
       <c r="H66" s="9">
-        <v>12.23</v>
-      </c>
-      <c r="I66" s="8">
-        <v>-1.75</v>
+        <v>12.36</v>
+      </c>
+      <c r="I66" s="10">
+        <v>-0.53</v>
       </c>
       <c r="J66" s="8">
-        <v>-9.77</v>
+        <v>7.65</v>
       </c>
       <c r="K66" s="9">
-        <v>68.86</v>
-      </c>
-      <c r="L66" s="8">
-        <v>-4.55</v>
+        <v>81.22</v>
+      </c>
+      <c r="L66" s="10">
+        <v>-2.87</v>
       </c>
       <c r="M66" s="9">
-        <v>12.23</v>
-      </c>
-      <c r="N66" s="8">
-        <v>-1.75</v>
+        <v>12.36</v>
+      </c>
+      <c r="N66" s="10">
+        <v>-0.53</v>
       </c>
       <c r="O66" s="8">
-        <v>-9.77</v>
+        <v>7.65</v>
       </c>
       <c r="P66" s="9">
-        <v>68.86</v>
-      </c>
-      <c r="Q66" s="8">
-        <v>-4.55</v>
+        <v>81.22</v>
+      </c>
+      <c r="Q66" s="10">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
+        <v>42887</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H67" s="9">
+        <v>12.23</v>
+      </c>
+      <c r="I67" s="10">
+        <v>-1.75</v>
+      </c>
+      <c r="J67" s="10">
+        <v>-9.77</v>
+      </c>
+      <c r="K67" s="9">
+        <v>68.86</v>
+      </c>
+      <c r="L67" s="10">
+        <v>-4.55</v>
+      </c>
+      <c r="M67" s="9">
+        <v>12.23</v>
+      </c>
+      <c r="N67" s="10">
+        <v>-1.75</v>
+      </c>
+      <c r="O67" s="10">
+        <v>-9.77</v>
+      </c>
+      <c r="P67" s="9">
+        <v>68.86</v>
+      </c>
+      <c r="Q67" s="10">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
         <v>42856</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H67" s="9">
+      <c r="B68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H68" s="9">
         <v>12.34</v>
       </c>
-      <c r="I67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="8">
+      <c r="I68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="10">
         <v>-2.7</v>
       </c>
-      <c r="K67" s="9">
+      <c r="K68" s="9">
         <v>56.63</v>
       </c>
-      <c r="L67" s="8">
+      <c r="L68" s="10">
         <v>-3.34</v>
       </c>
-      <c r="M67" s="9">
+      <c r="M68" s="9">
         <v>12.34</v>
       </c>
-      <c r="N67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O67" s="8">
+      <c r="N68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O68" s="10">
         <v>-2.7</v>
       </c>
-      <c r="P67" s="9">
+      <c r="P68" s="9">
         <v>56.63</v>
       </c>
-      <c r="Q67" s="8">
+      <c r="Q68" s="10">
         <v>-3.34</v>
       </c>
     </row>
@@ -4737,7 +4798,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>